--- a/output/pdf_financials_xlsx/ORIO.xlsx
+++ b/output/pdf_financials_xlsx/ORIO.xlsx
@@ -6631,13 +6631,13 @@
         <v>0</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>0.926</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>0.243</v>
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
@@ -11756,7 +11756,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -13682,7 +13686,11 @@
           <t>Revaluation reserve 6</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -15436,7 +15444,11 @@
           <t>Revaluation reserve 7</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -15542,7 +15554,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ORIO.xlsx
+++ b/output/pdf_financials_xlsx/ORIO.xlsx
@@ -993,19 +993,19 @@
         <v>0.710815</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3.528332</v>
+        <v>3.528</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>8.888</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>16.313</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>14.452</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>7.836</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>36.511</v>
@@ -66602,7 +66602,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -68960,7 +68960,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -71040,7 +71040,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -75454,7 +75454,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">

--- a/output/pdf_financials_xlsx/ORIO.xlsx
+++ b/output/pdf_financials_xlsx/ORIO.xlsx
@@ -1420,13 +1420,13 @@
         <v>-13.445</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-33.209</v>
+        <v>-33.441</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-165.678</v>
+        <v>-166.014</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-17.887</v>
+        <v>-18.287</v>
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
@@ -1485,13 +1485,13 @@
         <v>-0</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>0.232</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>0.336</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="R17" s="1" t="inlineStr">
         <is>
@@ -2267,13 +2267,13 @@
         <v>-13.445</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-33.209</v>
+        <v>-33.441</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-165.678</v>
+        <v>-166.014</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-17.887</v>
+        <v>-18.287</v>
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
@@ -2397,13 +2397,13 @@
         <v>-5.031</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-20.473</v>
+        <v>-20.705</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-153.042</v>
+        <v>-153.378</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-8.82</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2472,13 +2472,13 @@
         <v>-57.51028806584362</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-178.3362369337979</v>
+        <v>-180.3571428571429</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-673.926637016161</v>
+        <v>-675.4062266061914</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-47.51643141902812</v>
+        <v>-49.67137161943756</v>
       </c>
       <c r="R30" s="1" t="inlineStr">
         <is>
@@ -2537,13 +2537,13 @@
         <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.6937591579199187</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.2023925693013842</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.187346202220156</v>
       </c>
       <c r="R31" s="1" t="inlineStr">
         <is>
@@ -4751,34 +4751,28 @@
         <v>0</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.567</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>7.128</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>3.291</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>5.686</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.448</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>4.515</v>
+      </c>
+      <c r="S64" s="3" t="n">
+        <v>3.352</v>
       </c>
     </row>
     <row r="65">
@@ -4952,34 +4946,28 @@
         <v>0</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.072</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>2.801</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>2.423</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>7.068</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>6.441</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.797</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>7.458</v>
+      </c>
+      <c r="S67" s="3" t="n">
+        <v>6.432</v>
       </c>
     </row>
     <row r="68">
@@ -5027,16 +5015,16 @@
         </is>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>5.714</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>12.028</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0</v>
+        <v>12.127</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0</v>
+        <v>12.245</v>
       </c>
       <c r="R68" s="1" t="inlineStr">
         <is>
@@ -8041,10 +8029,10 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-7.928177</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-1.066252</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -8053,22 +8041,22 @@
         <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>-50.631</v>
+        <v>-49.542</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>-76.027</v>
+        <v>-26.567</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>-36.707</v>
+        <v>-3.949</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>-6</v>
+        <v>-1.841</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>-3.288</v>
+        <v>-0.414</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>-5.549</v>
+        <v>-2.224</v>
       </c>
       <c r="L114" s="3" t="n">
         <v>-5.933</v>
@@ -8106,37 +8094,37 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>4.143</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>3.085144</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.8259840000000001</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.159981</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>27.213</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>24.329</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>13.051</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>7.494</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>1.366</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>2.114</v>
@@ -8151,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.334</v>
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
@@ -8538,10 +8526,10 @@
         <v>0</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-1.627</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-1.122</v>
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
@@ -32948,7 +32936,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -33986,7 +33978,11 @@
           <t>Repurchase of common shares 25a</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -37100,7 +37096,11 @@
           <t>Repurchase of common shares 27a</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -38756,7 +38756,11 @@
           <t>Net cash (used in) generated from operating activities</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -41472,7 +41476,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -43640,7 +43648,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -43736,7 +43748,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -58672,7 +58688,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
           <t>-</t>
@@ -60988,7 +61008,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr">
         <is>
           <t>-</t>
@@ -61094,7 +61118,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
           <t>-</t>
@@ -62692,7 +62720,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E513" s="5" t="n">
         <v>4.143</v>
       </c>
@@ -62794,7 +62826,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E514" s="5" t="n">
         <v>-7.928177</v>
       </c>
@@ -65218,7 +65254,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E537" t="inlineStr">
         <is>
           <t>-</t>
@@ -67520,7 +67560,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E560" t="inlineStr">
         <is>
           <t>-</t>
@@ -71662,7 +71706,11 @@
           <t>Income tax recovery 17</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>
